--- a/docs/notifications.xlsx
+++ b/docs/notifications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dima\Desktop\Справочник\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503C1BF9-EC8F-495E-9F07-3AB43A4C1E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A5D73B9-765D-4278-9F9C-681ABBFE99A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,10 +36,10 @@
     <t>message</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
     <t>active</t>
-  </si>
-  <si>
-    <t>type (info, warning, error)</t>
   </si>
   <si>
     <t>Справочник находится в процессе разработки.</t>
@@ -390,10 +390,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">

--- a/docs/notifications.xlsx
+++ b/docs/notifications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dima\Desktop\Справочник\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A5D73B9-765D-4278-9F9C-681ABBFE99A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B79406-8A04-4870-B047-D7482E63B302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
